--- a/outputs/monitor_xlsx/20260310.xlsx
+++ b/outputs/monitor_xlsx/20260310.xlsx
@@ -1051,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="10" customWidth="1" style="8" min="1" max="1"/>
@@ -2359,41 +2359,46 @@
           <t>致茂</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="C23" t="n">
         <v>1360</v>
       </c>
+      <c r="D23" s="9" t="n">
+        <v>9.68</v>
+      </c>
       <c r="E23" s="5" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="F23" t="n">
         <v>2794</v>
       </c>
+      <c r="F23" s="10" t="n">
+        <v>1111</v>
+      </c>
       <c r="G23" s="6" t="n">
-        <v>1111</v>
+        <v>-473</v>
       </c>
       <c r="H23" t="n">
-        <v>-473</v>
+        <v>122</v>
       </c>
       <c r="I23" t="n">
-        <v>122</v>
+        <v>585</v>
       </c>
       <c r="J23" t="n">
-        <v>585</v>
+        <v>291</v>
       </c>
       <c r="K23" t="n">
-        <v>291</v>
+        <v>3176</v>
       </c>
       <c r="L23" t="n">
-        <v>3176</v>
+        <v>15391</v>
       </c>
       <c r="M23" t="n">
-        <v>15391</v>
+        <v>-106269</v>
       </c>
       <c r="N23" t="n">
-        <v>-106269</v>
-      </c>
-      <c r="O23" t="n">
-        <v>14.64</v>
+        <v>10.42</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2451,6 +2456,59 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5475</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="E25" t="n">
+        <v>514</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>-135</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-277</v>
+      </c>
+      <c r="H25" t="n">
+        <v>124</v>
+      </c>
+      <c r="I25" t="n">
+        <v>337</v>
+      </c>
+      <c r="J25" t="n">
+        <v>11</v>
+      </c>
+      <c r="K25" t="n">
+        <v>254</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1418</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-8951</v>
+      </c>
+      <c r="N25" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260310.xlsx
+++ b/outputs/monitor_xlsx/20260310.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4980" yWindow="-13680" windowWidth="21600" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="總覽" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,76 +12,41 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個股籌碼" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="7">
     <font>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="1"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="1"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="1"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="1"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="1"/>
-      <color rgb="FF008000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="3"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
+      <color rgb="00FF0000"/>
     </font>
     <font>
       <color rgb="00008000"/>
-    </font>
-    <font>
-      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -92,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCCC"/>
+        <fgColor rgb="00CCCCCC"/>
+        <bgColor rgb="00CCCCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,8 +81,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -127,15 +96,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -498,56 +461,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="8" min="1" max="8"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" s="8">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>台灣股市風險監控報告 - 20260310</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>類別</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>當日數值</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>單日變動</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>5日平均</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>5日總和</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>20日平均</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>20日總和</t>
         </is>
@@ -556,220 +526,236 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>32771.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.10%</t>
-        </is>
-      </c>
+          <t>+2.06%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5217.1$</t>
+          <t>297.53</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+2.47%</t>
-        </is>
-      </c>
+          <t>+2.97%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32696.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
+          <t>+2.49%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7865.12</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.70%</t>
-        </is>
-      </c>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>5229.7$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-2.24%</t>
-        </is>
-      </c>
+          <t>+2.71%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>原物料</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI原油期貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>82.69$</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-12.75%</t>
-        </is>
-      </c>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-250.86億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-658.5億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-3292.5億</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-194.12億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-3882.4億</t>
-        </is>
-      </c>
+          <t>7865.12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+0.70%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>130.59億</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>109.97億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>549.85億</t>
-        </is>
-      </c>
+          <t>24.93</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-2.24%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>112.73%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>125.68%</t>
-        </is>
-      </c>
+          <t>83.45$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-11.94%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -779,12 +765,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-154.93億</t>
+          <t>-250.86億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-658.5億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-3292.5億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-194.12億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-3882.4億</t>
         </is>
       </c>
     </row>
@@ -796,52 +803,135 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>投信現貨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11867口</t>
-        </is>
-      </c>
+          <t>130.59億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17660口</t>
-        </is>
-      </c>
+          <t>109.97億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>549.85億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-154.93億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11867口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>17660口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>23.93億</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>23.38億</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>116.89億</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>-0.03億</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>-0.59億</t>
         </is>
@@ -862,21 +952,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" style="8" min="1" max="1"/>
-    <col width="20" customWidth="1" style="8" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="8">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>詳細歷史統計數據</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>三大法人買賣超（過去20日）</t>
         </is>
@@ -930,6 +1020,10 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -955,7 +1049,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>融資融券變化（過去20日）</t>
         </is>
@@ -1010,7 +1104,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>期貨與選擇權（過去5日）</t>
         </is>
@@ -1024,7 +1118,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>125.68%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -1051,144 +1145,147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A1:V16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="8" min="1" max="1"/>
-    <col width="12" customWidth="1" style="8" min="2" max="2"/>
-    <col width="10" customWidth="1" style="8" min="3" max="5"/>
-    <col width="12" customWidth="1" style="8" min="6" max="6"/>
-    <col width="14" customWidth="1" style="8" min="7" max="11"/>
-    <col width="12" customWidth="1" style="8" min="12" max="15"/>
-    <col width="14" customWidth="1" style="8" min="16" max="16"/>
-    <col width="12" customWidth="1" style="8" min="17" max="17"/>
-    <col width="14" customWidth="1" style="8" min="18" max="19"/>
-    <col width="12" customWidth="1" style="8" min="20" max="20"/>
-    <col width="10" customWidth="1" style="8" min="21" max="21"/>
-    <col width="12" customWidth="1" style="8" min="22" max="22"/>
-    <col width="10" customWidth="1" style="8" min="23" max="23"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" s="8">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>個股籌碼監控報告 - 20260310</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>市場別</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>漲跌幅(%)</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>成交量(張)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>外資當日(張)</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>外資5日累計</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>投信當日(張)</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>投信5日累計</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>自營商當日(張)</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>融資增減(張)</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>融資5日累計</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>借券增減(張)</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>MA20乖離(%)</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>籌碼評價</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>買賣券商差</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>籌碼集中度5D(%)</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>借券賣出餘額</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>短回補天數</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>VWAP20D</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>VWAP乖離(%)</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1213,23 +1310,23 @@
       <c r="D4" t="n">
         <v>75.2</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>2.17</v>
       </c>
       <c r="F4" t="n">
         <v>173870</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>-40263</v>
       </c>
       <c r="H4" t="n">
-        <v>-623741</v>
+        <v>-287756</v>
       </c>
       <c r="I4" t="n">
         <v>3300</v>
       </c>
       <c r="J4" t="n">
-        <v>15820</v>
+        <v>9515</v>
       </c>
       <c r="K4" t="n">
         <v>43363</v>
@@ -1238,20 +1335,12 @@
         <v>13739</v>
       </c>
       <c r="M4" t="n">
-        <v>56889</v>
+        <v>48492</v>
       </c>
       <c r="N4" t="n">
         <v>-4406015</v>
       </c>
-      <c r="O4" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1260,41 +1349,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>-264</v>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>912</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3252</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-121</v>
       </c>
       <c r="H5" t="n">
-        <v>-201</v>
+        <v>-1556</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-104</v>
       </c>
       <c r="K5" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>9363</v>
+        <v>2744</v>
       </c>
       <c r="M5" t="n">
-        <v>49945</v>
+        <v>11277</v>
       </c>
       <c r="N5" t="n">
-        <v>-26678</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>-78823</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1303,12 +1404,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1317,47 +1418,39 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>912</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>4.71</v>
+        <v>1290</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>5.74</v>
       </c>
       <c r="F6" t="n">
-        <v>3252</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>-121</v>
+        <v>12096</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>140</v>
       </c>
       <c r="H6" t="n">
-        <v>-1798</v>
+        <v>-3403</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>844</v>
       </c>
       <c r="J6" t="n">
-        <v>-587</v>
+        <v>1230</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>472</v>
       </c>
       <c r="L6" t="n">
-        <v>2744</v>
+        <v>5785</v>
       </c>
       <c r="M6" t="n">
-        <v>14099</v>
+        <v>23095</v>
       </c>
       <c r="N6" t="n">
-        <v>-78823</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>-649004</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1366,12 +1459,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1380,47 +1473,39 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1290</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>5.74</v>
+        <v>1850</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2.21</v>
       </c>
       <c r="F7" t="n">
-        <v>12096</v>
+        <v>46926</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>140</v>
+        <v>-969</v>
       </c>
       <c r="H7" t="n">
-        <v>-4814</v>
+        <v>-48037</v>
       </c>
       <c r="I7" t="n">
-        <v>844</v>
+        <v>522</v>
       </c>
       <c r="J7" t="n">
-        <v>1322</v>
+        <v>3906</v>
       </c>
       <c r="K7" t="n">
-        <v>472</v>
+        <v>1723</v>
       </c>
       <c r="L7" t="n">
-        <v>5785</v>
+        <v>24570</v>
       </c>
       <c r="M7" t="n">
-        <v>28775</v>
+        <v>94073</v>
       </c>
       <c r="N7" t="n">
-        <v>-649004</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+        <v>-6482992</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1429,12 +1514,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1443,47 +1528,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1850</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2.21</v>
+        <v>1435</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>3.99</v>
       </c>
       <c r="F8" t="n">
-        <v>46926</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>-969</v>
+        <v>5374</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-307</v>
       </c>
       <c r="H8" t="n">
-        <v>-107069</v>
+        <v>185</v>
       </c>
       <c r="I8" t="n">
-        <v>522</v>
+        <v>111</v>
       </c>
       <c r="J8" t="n">
-        <v>7847</v>
+        <v>156</v>
       </c>
       <c r="K8" t="n">
-        <v>1723</v>
+        <v>107</v>
       </c>
       <c r="L8" t="n">
-        <v>24570</v>
+        <v>1833</v>
       </c>
       <c r="M8" t="n">
-        <v>116408</v>
+        <v>7336</v>
       </c>
       <c r="N8" t="n">
-        <v>-6482992</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140175</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1492,12 +1569,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1506,47 +1583,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>4.46</v>
+        <v>1360</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>9.68</v>
       </c>
       <c r="F9" t="n">
-        <v>164291</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>-27350</v>
+        <v>2794</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1111</v>
       </c>
       <c r="H9" t="n">
-        <v>1259</v>
+        <v>-1354</v>
       </c>
       <c r="I9" t="n">
-        <v>-146</v>
+        <v>122</v>
       </c>
       <c r="J9" t="n">
-        <v>-6620</v>
+        <v>423</v>
       </c>
       <c r="K9" t="n">
-        <v>4861</v>
+        <v>291</v>
       </c>
       <c r="L9" t="n">
-        <v>121046</v>
+        <v>3176</v>
       </c>
       <c r="M9" t="n">
-        <v>627307</v>
+        <v>12215</v>
       </c>
       <c r="N9" t="n">
-        <v>-1114110</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106269</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1571,23 +1640,23 @@
       <c r="D10" t="n">
         <v>2375</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>3065</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>313</v>
       </c>
       <c r="H10" t="n">
-        <v>-1714</v>
+        <v>-1342</v>
       </c>
       <c r="I10" t="n">
         <v>277</v>
       </c>
       <c r="J10" t="n">
-        <v>1090</v>
+        <v>894</v>
       </c>
       <c r="K10" t="n">
         <v>186</v>
@@ -1596,20 +1665,12 @@
         <v>1662</v>
       </c>
       <c r="M10" t="n">
-        <v>9060</v>
+        <v>7207</v>
       </c>
       <c r="N10" t="n">
         <v>-89495</v>
       </c>
-      <c r="O10" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1618,12 +1679,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1632,47 +1693,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3060</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>2.17</v>
+        <v>1705</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>-0.29</v>
       </c>
       <c r="F11" t="n">
-        <v>1835</v>
+        <v>1309</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4</v>
+        <v>-76</v>
       </c>
       <c r="H11" t="n">
-        <v>-1445</v>
+        <v>216</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>-208</v>
       </c>
       <c r="J11" t="n">
-        <v>193</v>
+        <v>-55</v>
       </c>
       <c r="K11" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L11" t="n">
-        <v>6032</v>
+        <v>4499</v>
       </c>
       <c r="M11" t="n">
-        <v>29877</v>
+        <v>18256</v>
       </c>
       <c r="N11" t="n">
-        <v>-19736</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-4.67</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19263</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1681,12 +1734,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1695,47 +1748,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1705</v>
+        <v>5475</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-0.29</v>
+        <v>9.94</v>
       </c>
       <c r="F12" t="n">
-        <v>1309</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>-76</v>
+        <v>514</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-135</v>
       </c>
       <c r="H12" t="n">
-        <v>249</v>
+        <v>64</v>
       </c>
       <c r="I12" t="n">
-        <v>-208</v>
+        <v>124</v>
       </c>
       <c r="J12" t="n">
-        <v>201</v>
+        <v>140</v>
       </c>
       <c r="K12" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>4499</v>
+        <v>254</v>
       </c>
       <c r="M12" t="n">
-        <v>22647</v>
+        <v>1164</v>
       </c>
       <c r="N12" t="n">
-        <v>-19263</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-14.92</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8951</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1758,25 +1803,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1485</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>10</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>8881</v>
-      </c>
-      <c r="G13" s="5" t="n">
+        <v>2730</v>
+      </c>
+      <c r="G13" s="6" t="n">
         <v>-563</v>
       </c>
       <c r="H13" t="n">
-        <v>-2114</v>
+        <v>-1805</v>
       </c>
       <c r="I13" t="n">
         <v>1434</v>
       </c>
       <c r="J13" t="n">
-        <v>1557</v>
+        <v>965</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
@@ -1785,20 +1830,12 @@
         <v>38</v>
       </c>
       <c r="M13" t="n">
-        <v>-195</v>
+        <v>96</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1807,12 +1844,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1821,47 +1858,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>129.5</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>4.02</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>2059</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>657</v>
+        <v>-4</v>
       </c>
       <c r="H14" t="n">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="I14" t="n">
-        <v>-301</v>
+        <v>-119</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-2284</v>
       </c>
       <c r="K14" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>-161</v>
+        <v>66</v>
       </c>
       <c r="M14" t="n">
-        <v>-160</v>
+        <v>124</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1870,12 +1899,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1884,47 +1913,39 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>349</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>2.2</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>4167</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>-4</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-247</v>
       </c>
       <c r="H15" t="n">
-        <v>628</v>
+        <v>1094</v>
       </c>
       <c r="I15" t="n">
-        <v>-119</v>
+        <v>144</v>
       </c>
       <c r="J15" t="n">
-        <v>-2164</v>
+        <v>307</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>-21</v>
       </c>
       <c r="L15" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="M15" t="n">
-        <v>-756</v>
+        <v>-319</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1933,12 +1954,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1947,568 +1968,41 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1150</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>-2.54</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>1178</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>-11</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>262</v>
       </c>
       <c r="H16" t="n">
-        <v>-1181</v>
+        <v>369</v>
       </c>
       <c r="I16" t="n">
-        <v>-72</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="L16" t="n">
-        <v>-92</v>
+        <v>-50</v>
       </c>
       <c r="M16" t="n">
-        <v>281</v>
+        <v>46</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>167</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3999</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-478</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>13</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3994</v>
-      </c>
-      <c r="M17" t="n">
-        <v>21875</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-11583</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-10.98</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1435</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>5374</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>-307</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>-906</v>
-      </c>
-      <c r="I18" t="n">
-        <v>111</v>
-      </c>
-      <c r="J18" t="n">
-        <v>434</v>
-      </c>
-      <c r="K18" t="n">
-        <v>107</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1833</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9169</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-140175</v>
-      </c>
-      <c r="O18" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>700</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="F19" t="n">
-        <v>931</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>-63</v>
-      </c>
-      <c r="H19" t="n">
-        <v>884</v>
-      </c>
-      <c r="I19" t="n">
-        <v>27</v>
-      </c>
-      <c r="J19" t="n">
-        <v>20</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-86</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-789</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1040</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>4100</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-944</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>-596</v>
-      </c>
-      <c r="I20" t="n">
-        <v>297</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1531</v>
-      </c>
-      <c r="K20" t="n">
-        <v>201</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2054</v>
-      </c>
-      <c r="M20" t="n">
-        <v>10360</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-47595</v>
-      </c>
-      <c r="O20" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>962</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>826</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>262</v>
-      </c>
-      <c r="H21" t="n">
-        <v>515</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>18</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-50</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>624</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2040</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-247</v>
-      </c>
-      <c r="H22" t="n">
-        <v>929</v>
-      </c>
-      <c r="I22" t="n">
-        <v>144</v>
-      </c>
-      <c r="J22" t="n">
-        <v>451</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-21</v>
-      </c>
-      <c r="L22" t="n">
-        <v>18</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-301</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1360</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>2794</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>1111</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>-473</v>
-      </c>
-      <c r="H23" t="n">
-        <v>122</v>
-      </c>
-      <c r="I23" t="n">
-        <v>585</v>
-      </c>
-      <c r="J23" t="n">
-        <v>291</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3176</v>
-      </c>
-      <c r="L23" t="n">
-        <v>15391</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-106269</v>
-      </c>
-      <c r="N23" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>245</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6087</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>72</v>
-      </c>
-      <c r="G24" t="n">
-        <v>345</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>101</v>
-      </c>
-      <c r="J24" t="n">
-        <v>156</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6910</v>
-      </c>
-      <c r="L24" t="n">
-        <v>34944</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-58894</v>
-      </c>
-      <c r="N24" t="n">
-        <v>17.38</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5475</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="E25" t="n">
-        <v>514</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>-135</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-277</v>
-      </c>
-      <c r="H25" t="n">
-        <v>124</v>
-      </c>
-      <c r="I25" t="n">
-        <v>337</v>
-      </c>
-      <c r="J25" t="n">
-        <v>11</v>
-      </c>
-      <c r="K25" t="n">
-        <v>254</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1418</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-8951</v>
-      </c>
-      <c r="N25" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260310.xlsx
+++ b/outputs/monitor_xlsx/20260310.xlsx
@@ -544,10 +544,6 @@
           <t>+2.06%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+2.97%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+2.49%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.10%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+2.71%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.01%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+0.70%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-2.24%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-11.94%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>-250.86億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-658.5億</t>
@@ -811,7 +774,6 @@
           <t>130.59億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>109.97億</t>
@@ -822,8 +784,6 @@
           <t>549.85億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>-154.93億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>11867口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>17660口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>23.93億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>23.38億</t>
@@ -1020,10 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1121,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1299,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>75.2</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2.17</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>173870</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-40263</v>
       </c>
       <c r="H4" t="n">
-        <v>-287756</v>
+        <v>-528197</v>
       </c>
       <c r="I4" t="n">
         <v>3300</v>
       </c>
       <c r="J4" t="n">
-        <v>9515</v>
+        <v>17763</v>
       </c>
       <c r="K4" t="n">
         <v>43363</v>
@@ -1335,11 +1278,14 @@
         <v>13739</v>
       </c>
       <c r="M4" t="n">
-        <v>48492</v>
+        <v>62231</v>
       </c>
       <c r="N4" t="n">
         <v>-4406015</v>
       </c>
+      <c r="O4" t="n">
+        <v>-0.88</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1362,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>912</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>4.71</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>3252</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>-121</v>
       </c>
       <c r="H5" t="n">
-        <v>-1556</v>
+        <v>-1680</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>-104</v>
+        <v>-453</v>
       </c>
       <c r="K5" t="n">
         <v>30</v>
@@ -1390,11 +1336,14 @@
         <v>2744</v>
       </c>
       <c r="M5" t="n">
-        <v>11277</v>
+        <v>14021</v>
       </c>
       <c r="N5" t="n">
         <v>-78823</v>
       </c>
+      <c r="O5" t="n">
+        <v>-5.09</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1417,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1290</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>5.74</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>12096</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>140</v>
       </c>
       <c r="H6" t="n">
-        <v>-3403</v>
+        <v>-2609</v>
       </c>
       <c r="I6" t="n">
         <v>844</v>
       </c>
       <c r="J6" t="n">
-        <v>1230</v>
+        <v>2342</v>
       </c>
       <c r="K6" t="n">
         <v>472</v>
@@ -1445,11 +1394,14 @@
         <v>5785</v>
       </c>
       <c r="M6" t="n">
-        <v>23095</v>
+        <v>28880</v>
       </c>
       <c r="N6" t="n">
         <v>-649004</v>
       </c>
+      <c r="O6" t="n">
+        <v>1.2</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1472,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1850</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>2.21</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>46926</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>-969</v>
       </c>
       <c r="H7" t="n">
-        <v>-48037</v>
+        <v>-86843</v>
       </c>
       <c r="I7" t="n">
         <v>522</v>
       </c>
       <c r="J7" t="n">
-        <v>3906</v>
+        <v>7090</v>
       </c>
       <c r="K7" t="n">
         <v>1723</v>
@@ -1500,11 +1452,14 @@
         <v>24570</v>
       </c>
       <c r="M7" t="n">
-        <v>94073</v>
+        <v>118643</v>
       </c>
       <c r="N7" t="n">
         <v>-6482992</v>
       </c>
+      <c r="O7" t="n">
+        <v>-1.02</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1527,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1435</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>3.99</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>5374</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>-307</v>
       </c>
       <c r="H8" t="n">
-        <v>185</v>
+        <v>-906</v>
       </c>
       <c r="I8" t="n">
         <v>111</v>
       </c>
       <c r="J8" t="n">
-        <v>156</v>
+        <v>434</v>
       </c>
       <c r="K8" t="n">
         <v>107</v>
@@ -1555,11 +1510,14 @@
         <v>1833</v>
       </c>
       <c r="M8" t="n">
-        <v>7336</v>
+        <v>9169</v>
       </c>
       <c r="N8" t="n">
         <v>-140175</v>
       </c>
+      <c r="O8" t="n">
+        <v>7.98</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1582,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1360</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>9.68</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>2794</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1111</v>
       </c>
       <c r="H9" t="n">
-        <v>-1354</v>
+        <v>-473</v>
       </c>
       <c r="I9" t="n">
         <v>122</v>
       </c>
       <c r="J9" t="n">
-        <v>423</v>
+        <v>585</v>
       </c>
       <c r="K9" t="n">
         <v>291</v>
@@ -1610,11 +1568,14 @@
         <v>3176</v>
       </c>
       <c r="M9" t="n">
-        <v>12215</v>
+        <v>15391</v>
       </c>
       <c r="N9" t="n">
         <v>-106269</v>
       </c>
+      <c r="O9" t="n">
+        <v>14.64</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1637,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2375</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3065</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>313</v>
       </c>
       <c r="H10" t="n">
-        <v>-1342</v>
+        <v>-1356</v>
       </c>
       <c r="I10" t="n">
         <v>277</v>
       </c>
       <c r="J10" t="n">
-        <v>894</v>
+        <v>1344</v>
       </c>
       <c r="K10" t="n">
         <v>186</v>
@@ -1665,11 +1626,14 @@
         <v>1662</v>
       </c>
       <c r="M10" t="n">
-        <v>7207</v>
+        <v>8869</v>
       </c>
       <c r="N10" t="n">
         <v>-89495</v>
       </c>
+      <c r="O10" t="n">
+        <v>9.98</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1692,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>1705</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>-0.29</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>1309</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>-76</v>
       </c>
       <c r="H11" t="n">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="I11" t="n">
         <v>-208</v>
       </c>
       <c r="J11" t="n">
-        <v>-55</v>
+        <v>-264</v>
       </c>
       <c r="K11" t="n">
         <v>80</v>
@@ -1720,11 +1684,14 @@
         <v>4499</v>
       </c>
       <c r="M11" t="n">
-        <v>18256</v>
+        <v>22755</v>
       </c>
       <c r="N11" t="n">
         <v>-19263</v>
       </c>
+      <c r="O11" t="n">
+        <v>-12.09</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1747,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>5475</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>9.94</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>514</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>-135</v>
       </c>
       <c r="H12" t="n">
-        <v>64</v>
+        <v>-277</v>
       </c>
       <c r="I12" t="n">
         <v>124</v>
       </c>
       <c r="J12" t="n">
-        <v>140</v>
+        <v>337</v>
       </c>
       <c r="K12" t="n">
         <v>11</v>
@@ -1775,11 +1742,14 @@
         <v>254</v>
       </c>
       <c r="M12" t="n">
-        <v>1164</v>
+        <v>1418</v>
       </c>
       <c r="N12" t="n">
         <v>-8951</v>
       </c>
+      <c r="O12" t="n">
+        <v>15.72</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1802,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-563</v>
       </c>
       <c r="H13" t="n">
-        <v>-1805</v>
+        <v>-3045</v>
       </c>
       <c r="I13" t="n">
         <v>1434</v>
       </c>
       <c r="J13" t="n">
-        <v>965</v>
+        <v>2655</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
@@ -1830,11 +1800,14 @@
         <v>38</v>
       </c>
       <c r="M13" t="n">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1857,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-4</v>
       </c>
       <c r="H14" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I14" t="n">
         <v>-119</v>
       </c>
       <c r="J14" t="n">
-        <v>-2284</v>
+        <v>-2403</v>
       </c>
       <c r="K14" t="n">
         <v>8</v>
@@ -1885,11 +1858,14 @@
         <v>66</v>
       </c>
       <c r="M14" t="n">
-        <v>124</v>
+        <v>190</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1912,26 +1888,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>-247</v>
       </c>
       <c r="H15" t="n">
-        <v>1094</v>
+        <v>929</v>
       </c>
       <c r="I15" t="n">
         <v>144</v>
       </c>
       <c r="J15" t="n">
-        <v>307</v>
+        <v>451</v>
       </c>
       <c r="K15" t="n">
         <v>-21</v>
@@ -1940,11 +1916,14 @@
         <v>18</v>
       </c>
       <c r="M15" t="n">
-        <v>-319</v>
+        <v>-301</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1967,26 +1946,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>262</v>
       </c>
       <c r="H16" t="n">
-        <v>369</v>
+        <v>515</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
         <v>-10</v>
@@ -1995,15 +1974,71 @@
         <v>-50</v>
       </c>
       <c r="M16" t="n">
-        <v>46</v>
+        <v>-4</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>294</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>1460</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-198</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1063</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-149</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6972</v>
+      </c>
+      <c r="M17" t="n">
+        <v>33781</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-22097</v>
+      </c>
+      <c r="O17" t="n">
+        <v>12.18</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260310.xlsx
+++ b/outputs/monitor_xlsx/20260310.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>12.18</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1705</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5620</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-593</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-8441</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-109</v>
+      </c>
+      <c r="J18" t="n">
+        <v>646</v>
+      </c>
+      <c r="K18" t="n">
+        <v>221</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5730</v>
+      </c>
+      <c r="M18" t="n">
+        <v>28987</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400939</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-3.32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>424</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15566</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>2268</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-5459</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-14</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-947</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1336</v>
+      </c>
+      <c r="L19" t="n">
+        <v>36578</v>
+      </c>
+      <c r="M19" t="n">
+        <v>193472</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-392447</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>428</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3807</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2250</v>
+      </c>
+      <c r="I20" t="n">
+        <v>41</v>
+      </c>
+      <c r="J20" t="n">
+        <v>611</v>
+      </c>
+      <c r="K20" t="n">
+        <v>516</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8899</v>
+      </c>
+      <c r="M20" t="n">
+        <v>48688</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161541</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
